--- a/backend/data/input/trades/test_mappings.xlsx
+++ b/backend/data/input/trades/test_mappings.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,66 +453,110 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PRLV SEPA</t>
+          <t>TEST VALID 1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CHARGES</t>
+          <t>Adhésion Organisme de Gestion Agréé (OGA)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FRAIS BANCAIRES</t>
+          <t>Autres dépenses</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PRLV</t>
+          <t>Charges Déductibles</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VIR STRIPE</t>
+          <t>TEST VALID 2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PRODUITS</t>
+          <t>Adhésion Organisme de Gestion Agréé (OGA)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>REVENUS LOCATIFS</t>
+          <t>Autres dépenses</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>STRIPE</t>
+          <t>Charges Déductibles</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CARTE</t>
+          <t>TEST INVALID 1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CHARGES</t>
+          <t>INVALID_LEVEL1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FRAIS BANCAIRES</t>
+          <t>INVALID_LEVEL2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CARTE BLEUE</t>
+          <t>INVALID_LEVEL3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TEST INVALID 2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Adhésion Organisme de Gestion Agréé (OGA)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>INVALID_LEVEL2_COMBO</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>INVALID_LEVEL3_COMBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TEST VALID 3</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Adhésion Organisme de Gestion Agréé (OGA)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Autres dépenses</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Charges Déductibles</t>
         </is>
       </c>
     </row>
